--- a/ingecart-marketing-kit/FESPA 2026 RESULTADOS/leads_fespa2026_enriched_con_resultados.xlsx
+++ b/ingecart-marketing-kit/FESPA 2026 RESULTADOS/leads_fespa2026_enriched_con_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Inaki Senar\Documents\GitHub\IS-BACKOFFICE\ingecart-marketing-kit\FESPA 2026 RESULTADOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2393426-BA29-4886-B2F3-785E9BECC586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2C3C88-B4B5-41F9-B0FF-888965B444F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -933,7 +933,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,6 +967,13 @@
       <color rgb="FF333232"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1020,7 +1027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1081,6 +1088,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1821,7 +1829,7 @@
         <v>94</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="23" t="s">
         <v>114</v>
       </c>
       <c r="J2" s="3"/>
@@ -1903,7 +1911,7 @@
         <v>95</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="23" t="s">
         <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -1989,7 +1997,7 @@
       <c r="H4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="23" t="s">
         <v>118</v>
       </c>
       <c r="J4" s="3"/>
@@ -3398,6 +3406,9 @@
       <c r="AA23"/>
       <c r="AB23"/>
     </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="L26" s="24"/>
+    </row>
     <row r="49" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K49" s="1">
         <f>900*0.3</f>
@@ -3419,10 +3430,13 @@
     <hyperlink ref="I18" r:id="rId5" xr:uid="{B5119282-94ED-4306-BEB6-34A280435005}"/>
     <hyperlink ref="I19" r:id="rId6" xr:uid="{7775A908-B1B5-407A-8969-0B7C9C1ACEE6}"/>
     <hyperlink ref="I6" r:id="rId7" xr:uid="{D000A353-EA78-4FC8-976D-20DF87AA9B34}"/>
+    <hyperlink ref="I2" r:id="rId8" xr:uid="{235E25E3-1A07-46E5-A6B2-7908EEF330DB}"/>
+    <hyperlink ref="I3" r:id="rId9" xr:uid="{96E98597-82A1-405B-A6A2-11D017A45D78}"/>
+    <hyperlink ref="I4" r:id="rId10" xr:uid="{C3341EC1-6A28-45AC-9FE9-2647CDAD4FA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
--- a/ingecart-marketing-kit/FESPA 2026 RESULTADOS/leads_fespa2026_enriched_con_resultados.xlsx
+++ b/ingecart-marketing-kit/FESPA 2026 RESULTADOS/leads_fespa2026_enriched_con_resultados.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
